--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260501_204056.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260501_204056.xlsx
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260501_204056.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260501_204056.xlsx
@@ -6272,7 +6272,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
